--- a/reports/fd0e0657-9dee-4923-bc8e-319996a08cb6/2025/08/report_______________________________08_2025.xlsx
+++ b/reports/fd0e0657-9dee-4923-bc8e-319996a08cb6/2025/08/report_______________________________08_2025.xlsx
@@ -839,7 +839,7 @@
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>9</v>
